--- a/F1_score_tracker_ocean.xlsx
+++ b/F1_score_tracker_ocean.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\std\GR\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\std\GR\report\DATN_Trung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39903D3A-D00D-4E70-BC92-C6E22E40D962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C76AF3-FBFA-4473-8B4D-376845419A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>F1 Score Tracker — All Models &amp; Traits</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Dataset: Essays</t>
   </si>
   <si>
-    <t>P2P (llama3-8b)</t>
-  </si>
-  <si>
     <t>AVG</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>CoT</t>
-  </si>
-  <si>
-    <t>P2P (gpt4o-mini)</t>
   </si>
   <si>
     <t>llama3-8b</t>
@@ -263,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -393,24 +387,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -460,15 +441,24 @@
     <xf numFmtId="2" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -488,18 +478,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,7 +487,11 @@
   <dxfs count="4">
     <dxf>
       <font>
-        <strike val="0"/>
+        <u val="double"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <u/>
       </font>
     </dxf>
@@ -521,11 +503,7 @@
     </dxf>
     <dxf>
       <font>
-        <u val="double"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
+        <strike val="0"/>
         <u/>
       </font>
     </dxf>
@@ -789,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" customWidth="1"/>
@@ -799,103 +777,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="2" spans="1:18" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
     </row>
     <row r="4" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30" t="s">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30" t="s">
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30" t="s">
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30" t="s">
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="29" t="s">
-        <v>17</v>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="19" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
@@ -941,13 +919,13 @@
       <c r="Q5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="29"/>
+      <c r="R5" s="19"/>
     </row>
     <row r="6" spans="1:18" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="25"/>
+      <c r="A6" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="28"/>
       <c r="C6" s="9"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6">
@@ -979,10 +957,10 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="9">
         <v>0.56630000000000003</v>
       </c>
@@ -1000,7 +978,7 @@
         <v>0.51900000000000002</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" ref="H7:H18" si="1">IFERROR(AVERAGE(F7,G7),"")</f>
+        <f t="shared" ref="H7:H17" si="1">IFERROR(AVERAGE(F7,G7),"")</f>
         <v>0.53770000000000007</v>
       </c>
       <c r="I7" s="5">
@@ -1010,7 +988,7 @@
         <v>0.5</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" ref="K7:K18" si="2">IFERROR(AVERAGE(I7,J7),"")</f>
+        <f t="shared" ref="K7:K17" si="2">IFERROR(AVERAGE(I7,J7),"")</f>
         <v>0.52129999999999999</v>
       </c>
       <c r="L7" s="5">
@@ -1020,7 +998,7 @@
         <v>0.48549999999999999</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" ref="N7:N18" si="3">IFERROR(AVERAGE(L7,M7),"")</f>
+        <f t="shared" ref="N7:N17" si="3">IFERROR(AVERAGE(L7,M7),"")</f>
         <v>0.52844999999999998</v>
       </c>
       <c r="O7" s="5">
@@ -1030,19 +1008,19 @@
         <v>0.57609999999999995</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" ref="Q7:Q18" si="4">IFERROR(AVERAGE(O7,P7),"")</f>
+        <f t="shared" ref="Q7:Q17" si="4">IFERROR(AVERAGE(O7,P7),"")</f>
         <v>0.57694999999999996</v>
       </c>
       <c r="R7" s="8">
-        <f t="shared" ref="R7:R19" si="5" xml:space="preserve"> AVERAGE(E7,H7,K7,N7,Q7)</f>
+        <f t="shared" ref="R7:R14" si="5" xml:space="preserve"> AVERAGE(E7,H7,K7,N7,Q7)</f>
         <v>0.54542999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="9">
         <v>0.57089999999999996</v>
       </c>
@@ -1099,10 +1077,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="20"/>
+      <c r="B9" s="23"/>
       <c r="C9" s="9">
         <v>0.6391</v>
       </c>
@@ -1159,10 +1137,10 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="29"/>
       <c r="C10" s="9">
         <v>0.6593</v>
       </c>
@@ -1219,10 +1197,10 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="20"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="9">
         <v>0.50939999999999996</v>
       </c>
@@ -1279,11 +1257,11 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="C12" s="9">
         <v>0.57999999999999996</v>
@@ -1341,9 +1319,9 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9">
         <v>0.56999999999999995</v>
@@ -1401,9 +1379,9 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="22"/>
       <c r="B14" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="9">
         <v>0.47</v>
@@ -1461,69 +1439,69 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19"/>
+      <c r="A15" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="B15" s="10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C15" s="9">
-        <v>0.56999999999999995</v>
+        <v>0.44</v>
       </c>
       <c r="D15" s="5">
-        <v>0.57999999999999996</v>
+        <v>0.6</v>
       </c>
       <c r="E15" s="6">
-        <f>IFERROR(AVERAGE(C15,D15),"")</f>
-        <v>0.57499999999999996</v>
+        <f t="shared" ref="E15:E17" si="7">IFERROR(AVERAGE(C15,D15),"")</f>
+        <v>0.52</v>
       </c>
       <c r="F15" s="5">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G15" s="5">
         <v>0.66</v>
       </c>
       <c r="H15" s="6">
         <f t="shared" si="1"/>
-        <v>0.48499999999999999</v>
+        <v>0.47000000000000003</v>
       </c>
       <c r="I15" s="5">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="J15" s="5">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="2"/>
-        <v>0.57000000000000006</v>
+        <v>0.54</v>
       </c>
       <c r="L15" s="5">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="M15" s="5">
-        <v>0.56999999999999995</v>
+        <v>0.62</v>
       </c>
       <c r="N15" s="6">
         <f t="shared" si="3"/>
-        <v>0.54499999999999993</v>
+        <v>0.505</v>
       </c>
       <c r="O15" s="5">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="P15" s="5">
-        <v>777787778777777</v>
+        <v>0.33</v>
       </c>
       <c r="Q15" s="6">
         <f t="shared" si="4"/>
-        <v>388893889388888.81</v>
-      </c>
-      <c r="R15" s="13">
-        <f t="shared" ref="R15:R18" si="7" xml:space="preserve"> AVERAGE(E15,H15,K15,N15,Q15)</f>
-        <v>77778777877778.203</v>
+        <v>0.495</v>
+      </c>
+      <c r="R15" s="15">
+        <f t="shared" ref="R15:R17" si="8" xml:space="preserve"> AVERAGE(E15,H15,K15,N15,Q15)</f>
+        <v>0.50600000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>24</v>
-      </c>
+      <c r="A16" s="22"/>
       <c r="B16" s="10" t="s">
         <v>20</v>
       </c>
@@ -1531,241 +1509,187 @@
         <v>0.44</v>
       </c>
       <c r="D16" s="5">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" ref="E16:E18" si="8">IFERROR(AVERAGE(C16,D16),"")</f>
-        <v>0.52</v>
+        <f t="shared" si="7"/>
+        <v>0.53</v>
       </c>
       <c r="F16" s="5">
-        <v>0.28000000000000003</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G16" s="5">
-        <v>0.66</v>
+        <v>0.49</v>
       </c>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>0.47000000000000003</v>
+        <v>0.53</v>
       </c>
       <c r="I16" s="5">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="J16" s="5">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="2"/>
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="L16" s="5">
-        <v>0.39</v>
+        <v>0.6</v>
       </c>
       <c r="M16" s="5">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="N16" s="6">
         <f t="shared" si="3"/>
-        <v>0.505</v>
+        <v>0.56499999999999995</v>
       </c>
       <c r="O16" s="5">
-        <v>0.66</v>
+        <v>0.52</v>
       </c>
       <c r="P16" s="5">
-        <v>0.33</v>
+        <v>0.59</v>
       </c>
       <c r="Q16" s="6">
         <f t="shared" si="4"/>
-        <v>0.495</v>
-      </c>
-      <c r="R16" s="15">
-        <f t="shared" si="7"/>
-        <v>0.50600000000000001</v>
+        <v>0.55499999999999994</v>
+      </c>
+      <c r="R16" s="16">
+        <f t="shared" si="8"/>
+        <v>0.53799999999999992</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="9">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="D17" s="5">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="E17" s="6">
-        <f t="shared" si="8"/>
-        <v>0.53</v>
+        <f t="shared" si="7"/>
+        <v>0.505</v>
       </c>
       <c r="F17" s="5">
-        <v>0.56999999999999995</v>
+        <v>0.3</v>
       </c>
       <c r="G17" s="5">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="6">
         <f t="shared" si="1"/>
-        <v>0.53</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="I17" s="5">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="J17" s="5">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="K17" s="6">
         <f t="shared" si="2"/>
-        <v>0.51</v>
+        <v>0.55499999999999994</v>
       </c>
       <c r="L17" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="M17" s="5">
         <v>0.6</v>
-      </c>
-      <c r="M17" s="5">
-        <v>0.53</v>
       </c>
       <c r="N17" s="6">
         <f t="shared" si="3"/>
-        <v>0.56499999999999995</v>
+        <v>0.52</v>
       </c>
       <c r="O17" s="5">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="P17" s="5">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="Q17" s="6">
         <f t="shared" si="4"/>
-        <v>0.55499999999999994</v>
-      </c>
-      <c r="R17" s="16">
-        <f t="shared" si="7"/>
-        <v>0.53799999999999992</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0.42</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="E18" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="R17" s="15">
         <f t="shared" si="8"/>
-        <v>0.505</v>
-      </c>
-      <c r="F18" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0.48</v>
-      </c>
-      <c r="J18" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="K18" s="6">
-        <f t="shared" si="2"/>
-        <v>0.55499999999999994</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0.44</v>
-      </c>
-      <c r="M18" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="N18" s="6">
-        <f t="shared" si="3"/>
-        <v>0.52</v>
-      </c>
-      <c r="O18" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="P18" s="5">
-        <v>0.31</v>
-      </c>
-      <c r="Q18" s="6">
-        <f t="shared" si="4"/>
-        <v>0.48</v>
-      </c>
-      <c r="R18" s="15">
-        <f t="shared" si="7"/>
         <v>0.502</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19"/>
-      <c r="B19" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="9">
-        <v>0.69</v>
-      </c>
-      <c r="D19" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" ref="E19:E23" si="9">IFERROR(AVERAGE(C19,D19),"")</f>
-        <v>0.43499999999999994</v>
-      </c>
-      <c r="F19" s="5">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" ref="H19:H23" si="10">IFERROR(AVERAGE(F19,G19),"")</f>
-        <v>0.56499999999999995</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="J19" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="K19" s="6">
-        <f t="shared" ref="K19:K23" si="11">IFERROR(AVERAGE(I19,J19),"")</f>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="M19" s="5">
-        <v>0.54</v>
-      </c>
-      <c r="N19" s="6">
-        <f t="shared" ref="N19:N23" si="12">IFERROR(AVERAGE(L19,M19),"")</f>
-        <v>0.53500000000000003</v>
-      </c>
-      <c r="O19" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="P19" s="5">
-        <v>0.36</v>
-      </c>
-      <c r="Q19" s="6">
-        <f t="shared" ref="Q19:Q23" si="13">IFERROR(AVERAGE(O19,P19),"")</f>
-        <v>0.495</v>
-      </c>
-      <c r="R19" s="15">
-        <f t="shared" si="5"/>
-        <v>0.49400000000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
-        <v>25</v>
-      </c>
+    <row r="18" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4" t="str">
+        <f t="shared" ref="E18:E21" si="9">IFERROR(AVERAGE(C18,D18),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="4" t="str">
+        <f t="shared" ref="H18:H21" si="10">IFERROR(AVERAGE(F18,G18),"")</f>
+        <v/>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="4" t="str">
+        <f t="shared" ref="K18:K21" si="11">IFERROR(AVERAGE(I18,J18),"")</f>
+        <v/>
+      </c>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="4" t="str">
+        <f t="shared" ref="N18:N21" si="12">IFERROR(AVERAGE(L18,M18),"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="4" t="str">
+        <f t="shared" ref="Q18:Q21" si="13">IFERROR(AVERAGE(O18,P18),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="4" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="4" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="4" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="str">
@@ -1797,7 +1721,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -1830,74 +1754,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="1"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="1"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="4" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:Q2"/>
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="R4:R5"/>
@@ -1906,34 +1773,25 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
   </mergeCells>
+  <conditionalFormatting sqref="E6:E21">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>"E2=MAX($E$6:$E$100)"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F21">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>"F2=MAX($F$2:$F$100)"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C4:C1048576">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>C4=MAX($C$1:$C$106)</formula>
+    <cfRule type="expression" dxfId="1" priority="17">
+      <formula>C4=MAX($C$1:$C$104)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D1048576">
-    <cfRule type="expression" dxfId="2" priority="8">
-      <formula>D4=MAX($D$1:$D$106)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E23">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>"E2=MAX($E$6:$E$100)"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F23">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>"F2=MAX($F$2:$F$100)"</formula>
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>D4=MAX($D$1:$D$104)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
